--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][CI]Yearly_U_test.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][CI]Yearly_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sd_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mean_P2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sd_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>U_statistic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -488,28 +500,28 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>9.037186325917112</v>
+        <v>8.987023597445805</v>
       </c>
       <c r="D2" t="n">
-        <v>4.291338790065353</v>
+        <v>4.372641915370775</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>10.2096965794419</v>
+        <v>9.899049859403124</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08491194653791</v>
+        <v>2.016508003320792</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I2" t="n">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="J2" t="n">
-        <v>0.275713144064071</v>
+        <v>0.3935736089376658</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -528,31 +540,31 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>5.297409194979221</v>
+        <v>5.177339636705086</v>
       </c>
       <c r="D3" t="n">
-        <v>3.200979135271366</v>
+        <v>3.211351392045215</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>14.15016596780668</v>
+        <v>13.82118948381784</v>
       </c>
       <c r="G3" t="n">
-        <v>3.392440580855148</v>
+        <v>3.406330746834943</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I3" t="n">
         <v>16</v>
       </c>
       <c r="J3" t="n">
-        <v>1.427975195843672e-08</v>
+        <v>8.423651412628246e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.283925587531017e-07</v>
+        <v>2.527095423788474e-06</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -568,31 +580,31 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>8.028022746691413</v>
+        <v>7.81980269680341</v>
       </c>
       <c r="D4" t="n">
-        <v>3.478672931524158</v>
+        <v>3.394332166812263</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>12.89837611668268</v>
+        <v>12.54491115649627</v>
       </c>
       <c r="G4" t="n">
-        <v>3.313091912151882</v>
+        <v>3.153100111372405</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="J4" t="n">
-        <v>3.956591173644805e-05</v>
+        <v>6.530776518863952e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001186977352093442</v>
+        <v>0.001959232955659185</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -608,31 +620,31 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>7.878313408669837</v>
+        <v>7.661134421005085</v>
       </c>
       <c r="D5" t="n">
-        <v>3.392170089900928</v>
+        <v>3.287415527182218</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>16.49034847709978</v>
+        <v>16.48195219785623</v>
       </c>
       <c r="G5" t="n">
-        <v>1.631769139719063</v>
+        <v>1.324031569768926</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.681424888183732e-09</v>
+        <v>1.204611101179206e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.044274664551197e-08</v>
+        <v>3.613833303537619e-07</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -648,31 +660,31 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>10.07193357320675</v>
+        <v>9.874506834129141</v>
       </c>
       <c r="D6" t="n">
-        <v>4.412403878106216</v>
+        <v>4.39387030042269</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>13.29845014027141</v>
+        <v>13.05592467648407</v>
       </c>
       <c r="G6" t="n">
-        <v>2.167442512142799</v>
+        <v>2.172975509104399</v>
       </c>
       <c r="H6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005270804155809905</v>
+        <v>0.00570589296217071</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1581241246742972</v>
+        <v>0.1711767888651213</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -688,31 +700,31 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>5.937090043810843</v>
+        <v>5.52528989117517</v>
       </c>
       <c r="D7" t="n">
-        <v>3.8115943269129</v>
+        <v>3.300622816210897</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>10.86419423811601</v>
+        <v>10.42568419603704</v>
       </c>
       <c r="G7" t="n">
-        <v>2.11897334921831</v>
+        <v>1.869107180835884</v>
       </c>
       <c r="H7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="J7" t="n">
-        <v>7.821959720561394e-06</v>
+        <v>5.658004990938262e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002346587916168418</v>
+        <v>0.0001697401497281479</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -728,31 +740,31 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>7.396684990066067</v>
+        <v>7.24197022913017</v>
       </c>
       <c r="D8" t="n">
-        <v>2.817417994992788</v>
+        <v>2.769507399128487</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>13.74747356323327</v>
+        <v>13.39085897616826</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46871311393129</v>
+        <v>2.315064316117873</v>
       </c>
       <c r="H8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J8" t="n">
-        <v>3.202307877618172e-08</v>
+        <v>1.082448896390599e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>9.606923632854515e-07</v>
+        <v>3.247346689171796e-06</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -768,31 +780,31 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>8.501465895448959</v>
+        <v>8.234234486254358</v>
       </c>
       <c r="D9" t="n">
-        <v>5.472310879052367</v>
+        <v>5.42297229113024</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>13.93068261111819</v>
+        <v>13.85733695589204</v>
       </c>
       <c r="G9" t="n">
-        <v>2.728161204259542</v>
+        <v>2.340428147906027</v>
       </c>
       <c r="H9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I9" t="n">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000448106693982186</v>
+        <v>0.0001994170717347799</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01344320081946558</v>
+        <v>0.005982512152043398</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -808,31 +820,31 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>8.806280927991347</v>
+        <v>8.504236557809195</v>
       </c>
       <c r="D10" t="n">
-        <v>3.942087248513425</v>
+        <v>3.729180070387814</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>14.70359872811508</v>
+        <v>14.6042705055897</v>
       </c>
       <c r="G10" t="n">
-        <v>2.575202661564179</v>
+        <v>2.438703903664829</v>
       </c>
       <c r="H10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="J10" t="n">
-        <v>4.026689709618671e-06</v>
+        <v>3.278773194246992e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0001208006912885601</v>
+        <v>9.836319582740976e-05</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -848,31 +860,31 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>8.896509383294886</v>
+        <v>8.623169654262568</v>
       </c>
       <c r="D11" t="n">
-        <v>3.07612061546259</v>
+        <v>2.82646854559251</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>15.26281602809997</v>
+        <v>14.74164904649121</v>
       </c>
       <c r="G11" t="n">
-        <v>3.638295074010517</v>
+        <v>3.555254126725502</v>
       </c>
       <c r="H11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="J11" t="n">
-        <v>5.898368645783022e-06</v>
+        <v>1.992115150887319e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0001769510593734907</v>
+        <v>0.0005976345452661956</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -888,31 +900,31 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>8.053089224700161</v>
+        <v>8.17153133558349</v>
       </c>
       <c r="D12" t="n">
-        <v>3.652593369180062</v>
+        <v>3.680573086242564</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>16.52852225664358</v>
+        <v>16.56771117728411</v>
       </c>
       <c r="G12" t="n">
-        <v>2.414949515722259</v>
+        <v>1.949048226638585</v>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>4.357951392321109e-09</v>
+        <v>1.37621980788932e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>1.307385417696333e-07</v>
+        <v>4.12865942366796e-07</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -928,28 +940,28 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>12.16906841696092</v>
+        <v>12.19957935052206</v>
       </c>
       <c r="D13" t="n">
-        <v>3.014981146358248</v>
+        <v>3.073368351542603</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>12.08477097944382</v>
+        <v>11.50582551314134</v>
       </c>
       <c r="G13" t="n">
-        <v>2.881210228012054</v>
+        <v>2.140202498409018</v>
       </c>
       <c r="H13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I13" t="n">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5028577901906203</v>
+        <v>0.2900957321337637</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -968,31 +980,31 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>7.660321032840511</v>
+        <v>7.568939350989226</v>
       </c>
       <c r="D14" t="n">
-        <v>2.798460651600596</v>
+        <v>2.819383675240766</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>13.13130244514587</v>
+        <v>12.51421494645698</v>
       </c>
       <c r="G14" t="n">
-        <v>4.752239874970373</v>
+        <v>4.768877499463487</v>
       </c>
       <c r="H14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001870873439028201</v>
+        <v>0.008038063309718787</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05612620317084602</v>
+        <v>0.2411418992915636</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -1008,31 +1020,31 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>11.4677969242683</v>
+        <v>11.59418202102174</v>
       </c>
       <c r="D15" t="n">
-        <v>2.300598152099117</v>
+        <v>2.261405175505013</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
-        <v>14.76535636708737</v>
+        <v>14.51409176825873</v>
       </c>
       <c r="G15" t="n">
-        <v>2.204653275757396</v>
+        <v>2.020486418627464</v>
       </c>
       <c r="H15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J15" t="n">
-        <v>9.423308823794465e-06</v>
+        <v>7.186887210782031e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0002826992647138339</v>
+        <v>0.002156066163234609</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -1048,31 +1060,31 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>8.807439898732378</v>
+        <v>8.511170999442745</v>
       </c>
       <c r="D16" t="n">
-        <v>3.237615282159517</v>
+        <v>2.953731125416112</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
-        <v>12.06956617545553</v>
+        <v>11.96686019715571</v>
       </c>
       <c r="G16" t="n">
-        <v>1.828542035464372</v>
+        <v>1.385174360792069</v>
       </c>
       <c r="H16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" t="n">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001506472847573664</v>
+        <v>4.431157606998368e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.004519418542720991</v>
+        <v>0.00132934728209951</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1088,31 +1100,31 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>10.74541664838739</v>
+        <v>10.67123500696159</v>
       </c>
       <c r="D17" t="n">
-        <v>3.258598578103503</v>
+        <v>3.305045812691045</v>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>15.01334489893657</v>
+        <v>15.01693568640733</v>
       </c>
       <c r="G17" t="n">
-        <v>3.037767385224753</v>
+        <v>3.232932336053235</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I17" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00013896679175973</v>
+        <v>0.000370151729784253</v>
       </c>
       <c r="K17" t="n">
-        <v>0.004169003752791901</v>
+        <v>0.01110455189352759</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1128,31 +1140,31 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>8.296468543560366</v>
+        <v>7.91707054400316</v>
       </c>
       <c r="D18" t="n">
-        <v>5.07821242581988</v>
+        <v>4.823295600533329</v>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
-        <v>13.81660124319343</v>
+        <v>13.72405580675514</v>
       </c>
       <c r="G18" t="n">
-        <v>3.142917070092351</v>
+        <v>3.209711104598691</v>
       </c>
       <c r="H18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="J18" t="n">
-        <v>9.22961211124175e-05</v>
+        <v>5.384804125890827e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.002768883633372525</v>
+        <v>0.001615441237767248</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1168,34 +1180,34 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>9.680531114691327</v>
+        <v>9.655688690937957</v>
       </c>
       <c r="D19" t="n">
-        <v>4.084114097074791</v>
+        <v>4.166480385856071</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>13.67869228341059</v>
+        <v>13.18966098635512</v>
       </c>
       <c r="G19" t="n">
-        <v>3.513094531074457</v>
+        <v>3.283548596474094</v>
       </c>
       <c r="H19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I19" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="J19" t="n">
-        <v>0.001524389376134469</v>
+        <v>0.00570589296217071</v>
       </c>
       <c r="K19" t="n">
-        <v>0.04573168128403408</v>
+        <v>0.1711767888651213</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1208,31 +1220,31 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>9.660865983612176</v>
+        <v>9.564418102871569</v>
       </c>
       <c r="D20" t="n">
-        <v>3.066326572943766</v>
+        <v>3.092178641878261</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>14.9891394213896</v>
+        <v>14.85681598660669</v>
       </c>
       <c r="G20" t="n">
-        <v>2.681485512614356</v>
+        <v>2.134221185341035</v>
       </c>
       <c r="H20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I20" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="J20" t="n">
-        <v>6.03792925041696e-07</v>
+        <v>1.06062188881748e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>1.811378775125088e-05</v>
+        <v>3.181865666452441e-05</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
@@ -1248,31 +1260,31 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>9.207141102675205</v>
+        <v>9.214952702233964</v>
       </c>
       <c r="D21" t="n">
-        <v>3.326707026675506</v>
+        <v>3.395081481476211</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
-        <v>14.1246800975278</v>
+        <v>12.98088357790328</v>
       </c>
       <c r="G21" t="n">
-        <v>3.652314518926139</v>
+        <v>2.111135947804097</v>
       </c>
       <c r="H21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I21" t="n">
         <v>85</v>
       </c>
       <c r="J21" t="n">
-        <v>1.786731182565398e-05</v>
+        <v>0.0001518610841054225</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0005360193547696194</v>
+        <v>0.004555832523162676</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
@@ -1288,31 +1300,31 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>7.155182413276783</v>
+        <v>7.029152357761116</v>
       </c>
       <c r="D22" t="n">
-        <v>2.655531140645865</v>
+        <v>2.636016534134482</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" t="n">
-        <v>16.89838497806435</v>
+        <v>16.61029726317865</v>
       </c>
       <c r="G22" t="n">
-        <v>3.192996215808021</v>
+        <v>3.272780660371904</v>
       </c>
       <c r="H22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I22" t="n">
         <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>2.681424888183732e-09</v>
+        <v>1.37621980788932e-08</v>
       </c>
       <c r="K22" t="n">
-        <v>8.044274664551197e-08</v>
+        <v>4.12865942366796e-07</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
@@ -1328,31 +1340,31 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>6.416558683549233</v>
+        <v>6.33276349787678</v>
       </c>
       <c r="D23" t="n">
-        <v>3.15504694013115</v>
+        <v>3.192732959234955</v>
       </c>
       <c r="E23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>12.06081384196815</v>
+        <v>11.22593825272844</v>
       </c>
       <c r="G23" t="n">
-        <v>3.225837227359835</v>
+        <v>1.91995625179725</v>
       </c>
       <c r="H23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J23" t="n">
-        <v>8.22296167687859e-07</v>
+        <v>5.658004990938262e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>2.466888503063577e-05</v>
+        <v>0.0001697401497281479</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1368,31 +1380,31 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>13.17973859576956</v>
+        <v>13.15247680334518</v>
       </c>
       <c r="D24" t="n">
-        <v>2.689508502886218</v>
+        <v>2.741581633547486</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" t="n">
-        <v>16.39846849888702</v>
+        <v>16.54008011225403</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99874228744007</v>
+        <v>1.735707557452864</v>
       </c>
       <c r="H24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I24" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="J24" t="n">
-        <v>7.187263180570752e-05</v>
+        <v>5.931636742376943e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.002156178954171225</v>
+        <v>0.001779491022713083</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -1408,34 +1420,34 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>9.583145474904599</v>
+        <v>9.626643949123816</v>
       </c>
       <c r="D25" t="n">
-        <v>3.63309835280419</v>
+        <v>3.701631513451608</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>14.02744060504599</v>
+        <v>13.14940424053927</v>
       </c>
       <c r="G25" t="n">
-        <v>3.40866675447295</v>
+        <v>2.645135031090147</v>
       </c>
       <c r="H25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I25" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0002622403088409687</v>
+        <v>0.001899688427521008</v>
       </c>
       <c r="K25" t="n">
-        <v>0.007867209265229059</v>
+        <v>0.05699065282563025</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1448,31 +1460,31 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>11.31823588142153</v>
+        <v>11.3582204972202</v>
       </c>
       <c r="D26" t="n">
-        <v>2.356106088715922</v>
+        <v>2.396365614771023</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>15.82364369884677</v>
+        <v>15.95036307679624</v>
       </c>
       <c r="G26" t="n">
-        <v>2.190897051687597</v>
+        <v>2.063616554186708</v>
       </c>
       <c r="H26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>4.01933742563528e-08</v>
+        <v>1.388167354759115e-07</v>
       </c>
       <c r="K26" t="n">
-        <v>1.205801227690584e-06</v>
+        <v>4.164502064277344e-06</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1488,31 +1500,31 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>5.570121979931876</v>
+        <v>5.44861093632164</v>
       </c>
       <c r="D27" t="n">
-        <v>3.728987623274457</v>
+        <v>3.757075309398495</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F27" t="n">
-        <v>15.05794368034829</v>
+        <v>15.03270739065961</v>
       </c>
       <c r="G27" t="n">
-        <v>2.569649248511864</v>
+        <v>2.572876119172824</v>
       </c>
       <c r="H27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>7.038642430349237e-09</v>
+        <v>3.922293064323379e-08</v>
       </c>
       <c r="K27" t="n">
-        <v>2.111592729104771e-07</v>
+        <v>1.176687919297014e-06</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1528,31 +1540,31 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>8.218032021515416</v>
+        <v>8.144133057724318</v>
       </c>
       <c r="D28" t="n">
-        <v>2.61697815313688</v>
+        <v>2.645260953102848</v>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F28" t="n">
-        <v>14.17366848463808</v>
+        <v>13.5778751512707</v>
       </c>
       <c r="G28" t="n">
-        <v>4.206545152270104</v>
+        <v>3.918338396309524</v>
       </c>
       <c r="H28" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I28" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J28" t="n">
-        <v>1.954729674583517e-05</v>
+        <v>9.549577577076511e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.000586418902375055</v>
+        <v>0.002864873273122953</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
@@ -1568,31 +1580,31 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>7.518531904761854</v>
+        <v>7.368084630480131</v>
       </c>
       <c r="D29" t="n">
-        <v>2.620155928949534</v>
+        <v>2.566205027994929</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>17.55771038190148</v>
+        <v>17.65534178553084</v>
       </c>
       <c r="G29" t="n">
-        <v>2.013886898421156</v>
+        <v>1.798778303058926</v>
       </c>
       <c r="H29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>2.681424888183732e-09</v>
+        <v>1.204611101179206e-08</v>
       </c>
       <c r="K29" t="n">
-        <v>8.044274664551197e-08</v>
+        <v>3.613833303537619e-07</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1608,31 +1620,31 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>9.384925921373165</v>
+        <v>9.038574246828132</v>
       </c>
       <c r="D30" t="n">
-        <v>5.631159717219479</v>
+        <v>5.480166149187427</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>15.85918397488971</v>
+        <v>14.95817093854689</v>
       </c>
       <c r="G30" t="n">
-        <v>4.900567521060871</v>
+        <v>4.577261349661152</v>
       </c>
       <c r="H30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I30" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0002834212197516381</v>
+        <v>0.0007915260256819307</v>
       </c>
       <c r="K30" t="n">
-        <v>0.008502636592549144</v>
+        <v>0.02374578077045792</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
@@ -1648,31 +1660,31 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>10.43718738396615</v>
+        <v>10.22635971338014</v>
       </c>
       <c r="D31" t="n">
-        <v>3.516616245163818</v>
+        <v>3.430839070007248</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F31" t="n">
-        <v>15.30144117635949</v>
+        <v>14.96608490366795</v>
       </c>
       <c r="G31" t="n">
-        <v>2.2336077439157</v>
+        <v>2.033689139897863</v>
       </c>
       <c r="H31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I31" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="J31" t="n">
-        <v>2.73205048921227e-06</v>
+        <v>5.078150611178878e-06</v>
       </c>
       <c r="K31" t="n">
-        <v>8.19615146763681e-05</v>
+        <v>0.0001523445183353663</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
@@ -1688,31 +1700,31 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>68.78855269441324</v>
+        <v>68.07256032297761</v>
       </c>
       <c r="D32" t="n">
-        <v>12.92129281970671</v>
+        <v>12.69253087078954</v>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F32" t="n">
-        <v>81.96380181680483</v>
+        <v>82.5321128123888</v>
       </c>
       <c r="G32" t="n">
-        <v>5.899340745096021</v>
+        <v>4.71615918759094</v>
       </c>
       <c r="H32" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I32" t="n">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="J32" t="n">
-        <v>0.000448106693982186</v>
+        <v>0.0002181597558826505</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01344320081946558</v>
+        <v>0.006544792676479515</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
@@ -1728,31 +1740,31 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>68.38310892286518</v>
+        <v>67.61446516244526</v>
       </c>
       <c r="D33" t="n">
-        <v>10.83088060334534</v>
+        <v>10.36462619489678</v>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F33" t="n">
-        <v>75.93732474158237</v>
+        <v>75.37030651016381</v>
       </c>
       <c r="G33" t="n">
-        <v>5.816290108229935</v>
+        <v>5.105103946496585</v>
       </c>
       <c r="H33" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I33" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="J33" t="n">
-        <v>0.002977997490474926</v>
+        <v>0.002774027680343255</v>
       </c>
       <c r="K33" t="n">
-        <v>0.08933992471424779</v>
+        <v>0.08322083041029765</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1768,31 +1780,31 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>73.10932355343871</v>
+        <v>73.59709822340413</v>
       </c>
       <c r="D34" t="n">
-        <v>8.529312786441453</v>
+        <v>8.356571610684409</v>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F34" t="n">
-        <v>82.16267477881932</v>
+        <v>83.85335780670954</v>
       </c>
       <c r="G34" t="n">
-        <v>7.12670585978237</v>
+        <v>5.851463592209966</v>
       </c>
       <c r="H34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I34" t="n">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0008684598407633108</v>
+        <v>0.0001994170717347799</v>
       </c>
       <c r="K34" t="n">
-        <v>0.02605379522289932</v>
+        <v>0.005982512152043398</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1808,28 +1820,28 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>78.13429823666712</v>
+        <v>78.37991179151913</v>
       </c>
       <c r="D35" t="n">
-        <v>7.450726361933312</v>
+        <v>7.504547154930959</v>
       </c>
       <c r="E35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F35" t="n">
-        <v>74.11444801018274</v>
+        <v>74.17345069294565</v>
       </c>
       <c r="G35" t="n">
-        <v>5.792208889923895</v>
+        <v>5.525563952483099</v>
       </c>
       <c r="H35" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I35" t="n">
-        <v>396</v>
+        <v>340</v>
       </c>
       <c r="J35" t="n">
-        <v>0.056133213319545</v>
+        <v>0.04651454657009027</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1848,31 +1860,31 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>72.08080634806511</v>
+        <v>71.71771585566236</v>
       </c>
       <c r="D36" t="n">
-        <v>9.291339727155403</v>
+        <v>9.307532846954857</v>
       </c>
       <c r="E36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F36" t="n">
-        <v>82.70805444479919</v>
+        <v>83.04084661305434</v>
       </c>
       <c r="G36" t="n">
-        <v>5.097123671898214</v>
+        <v>5.292931678132235</v>
       </c>
       <c r="H36" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I36" t="n">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0001181178248378447</v>
+        <v>0.0001518610841054225</v>
       </c>
       <c r="K36" t="n">
-        <v>0.003543534745135342</v>
+        <v>0.004555832523162676</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
@@ -1888,31 +1900,31 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>78.18702632988922</v>
+        <v>79.03226914156751</v>
       </c>
       <c r="D37" t="n">
-        <v>8.676444256902393</v>
+        <v>7.781805374188732</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>84.1829261026074</v>
+        <v>84.22566605504126</v>
       </c>
       <c r="G37" t="n">
-        <v>4.709046288660322</v>
+        <v>4.672499999766449</v>
       </c>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I37" t="n">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01277430952988634</v>
+        <v>0.02502914588509006</v>
       </c>
       <c r="K37" t="n">
-        <v>0.3832292858965903</v>
+        <v>0.7508743765527017</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -1928,28 +1940,28 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>73.09735650144215</v>
+        <v>73.57707282200461</v>
       </c>
       <c r="D38" t="n">
-        <v>10.22157079658438</v>
+        <v>10.15286513299584</v>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F38" t="n">
-        <v>78.73338507246503</v>
+        <v>78.65931296261417</v>
       </c>
       <c r="G38" t="n">
-        <v>6.051819395538726</v>
+        <v>6.252151178764048</v>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I38" t="n">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="J38" t="n">
-        <v>0.06148381785893191</v>
+        <v>0.1138369442691806</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1968,31 +1980,31 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>62.73408665112172</v>
+        <v>62.30587767992439</v>
       </c>
       <c r="D39" t="n">
-        <v>8.847191786337122</v>
+        <v>8.772120393604599</v>
       </c>
       <c r="E39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F39" t="n">
-        <v>71.56381637084269</v>
+        <v>71.56142622845962</v>
       </c>
       <c r="G39" t="n">
-        <v>8.118503532019028</v>
+        <v>7.538602708171368</v>
       </c>
       <c r="H39" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I39" t="n">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="J39" t="n">
-        <v>0.001524389376134469</v>
+        <v>0.001010851986690264</v>
       </c>
       <c r="K39" t="n">
-        <v>0.04573168128403408</v>
+        <v>0.03032555960070792</v>
       </c>
       <c r="L39" t="b">
         <v>1</v>
@@ -2008,28 +2020,28 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>70.34438990480903</v>
+        <v>70.99616950857627</v>
       </c>
       <c r="D40" t="n">
-        <v>9.161005045377257</v>
+        <v>8.763585512656679</v>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F40" t="n">
-        <v>72.48232096854213</v>
+        <v>72.11373940779357</v>
       </c>
       <c r="G40" t="n">
-        <v>6.907114141813593</v>
+        <v>7.262885101186829</v>
       </c>
       <c r="H40" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I40" t="n">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2186971048513838</v>
+        <v>0.4192903869887252</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -2048,28 +2060,28 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>75.7777856049691</v>
+        <v>75.97233974647548</v>
       </c>
       <c r="D41" t="n">
-        <v>10.45474623757869</v>
+        <v>10.62589640124103</v>
       </c>
       <c r="E41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F41" t="n">
-        <v>77.71810292789687</v>
+        <v>78.17225593874532</v>
       </c>
       <c r="G41" t="n">
-        <v>7.238069234897829</v>
+        <v>7.586739343710058</v>
       </c>
       <c r="H41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I41" t="n">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6100514617950388</v>
+        <v>0.6409355457337678</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -2088,28 +2100,28 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>76.53853055144367</v>
+        <v>76.83947829582087</v>
       </c>
       <c r="D42" t="n">
-        <v>9.470695587847123</v>
+        <v>9.548145862841297</v>
       </c>
       <c r="E42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F42" t="n">
-        <v>73.77789853800016</v>
+        <v>74.72790451846149</v>
       </c>
       <c r="G42" t="n">
-        <v>6.872661051929017</v>
+        <v>5.08103302428854</v>
       </c>
       <c r="H42" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I42" t="n">
-        <v>341</v>
+        <v>288</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4179401757432032</v>
+        <v>0.4192903869887252</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2128,31 +2140,31 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>58.91372524167389</v>
+        <v>59.31257076639034</v>
       </c>
       <c r="D43" t="n">
-        <v>7.456889577329685</v>
+        <v>7.34473565062192</v>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F43" t="n">
-        <v>81.70518705904648</v>
+        <v>81.88648054320096</v>
       </c>
       <c r="G43" t="n">
-        <v>4.661154419781409</v>
+        <v>4.528088177809086</v>
       </c>
       <c r="H43" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2.098410375666297e-09</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K43" t="n">
-        <v>6.295231126998892e-08</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2168,28 +2180,28 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>76.89487722152998</v>
+        <v>76.94974010602228</v>
       </c>
       <c r="D44" t="n">
-        <v>6.266453143314946</v>
+        <v>6.389786489903097</v>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F44" t="n">
-        <v>79.30747873428876</v>
+        <v>80.02969553543164</v>
       </c>
       <c r="G44" t="n">
-        <v>6.284807635065836</v>
+        <v>5.777412822562832</v>
       </c>
       <c r="H44" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I44" t="n">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="J44" t="n">
-        <v>0.275713144064071</v>
+        <v>0.1686908166290303</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -2208,31 +2220,31 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>66.59163436579513</v>
+        <v>65.65607514956695</v>
       </c>
       <c r="D45" t="n">
-        <v>11.90027659398588</v>
+        <v>11.20872418232872</v>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F45" t="n">
-        <v>79.37840569831913</v>
+        <v>80.83198728367435</v>
       </c>
       <c r="G45" t="n">
-        <v>7.528742447310249</v>
+        <v>6.345737612863777</v>
       </c>
       <c r="H45" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I45" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0004155596669612428</v>
+        <v>5.931636742376943e-05</v>
       </c>
       <c r="K45" t="n">
-        <v>0.01246679000883729</v>
+        <v>0.001779491022713083</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2248,31 +2260,31 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>66.47740619368115</v>
+        <v>66.53884902203464</v>
       </c>
       <c r="D46" t="n">
-        <v>10.10135089865012</v>
+        <v>10.30506978131769</v>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F46" t="n">
-        <v>81.02101465216901</v>
+        <v>81.35579944822732</v>
       </c>
       <c r="G46" t="n">
-        <v>5.508844683454935</v>
+        <v>4.828488027700167</v>
       </c>
       <c r="H46" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I46" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="J46" t="n">
-        <v>2.336913118941477e-05</v>
+        <v>5.384804125890827e-05</v>
       </c>
       <c r="K46" t="n">
-        <v>0.000701073935682443</v>
+        <v>0.001615441237767248</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
@@ -2288,31 +2300,31 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>63.60666402288221</v>
+        <v>63.48672302253632</v>
       </c>
       <c r="D47" t="n">
-        <v>9.214160515005075</v>
+        <v>9.385022073692255</v>
       </c>
       <c r="E47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F47" t="n">
-        <v>80.90448278681878</v>
+        <v>81.62399268287247</v>
       </c>
       <c r="G47" t="n">
-        <v>5.637313711433375</v>
+        <v>5.500970497508502</v>
       </c>
       <c r="H47" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I47" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="J47" t="n">
-        <v>4.418100645390863e-07</v>
+        <v>8.412531021150415e-07</v>
       </c>
       <c r="K47" t="n">
-        <v>1.325430193617259e-05</v>
+        <v>2.523759306345125e-05</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2328,31 +2340,31 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>70.8345764010905</v>
+        <v>71.42988014333237</v>
       </c>
       <c r="D48" t="n">
-        <v>12.27915728564757</v>
+        <v>12.17376048417507</v>
       </c>
       <c r="E48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F48" t="n">
-        <v>78.921769978748</v>
+        <v>78.39689727179397</v>
       </c>
       <c r="G48" t="n">
-        <v>6.806079334769021</v>
+        <v>5.959066937684901</v>
       </c>
       <c r="H48" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I48" t="n">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="J48" t="n">
-        <v>0.02710516229283997</v>
+        <v>0.07410948534781449</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8131548687851989</v>
+        <v>1</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2368,34 +2380,34 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>75.62389825596868</v>
+        <v>75.25429119013644</v>
       </c>
       <c r="D49" t="n">
-        <v>8.025824064249575</v>
+        <v>7.980133321487913</v>
       </c>
       <c r="E49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
-        <v>81.79535512116372</v>
+        <v>83.43812807667685</v>
       </c>
       <c r="G49" t="n">
-        <v>9.111111802865031</v>
+        <v>8.078209917878612</v>
       </c>
       <c r="H49" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I49" t="n">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01077229190813337</v>
+        <v>0.00150491077133161</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3231687572440012</v>
+        <v>0.04514732313994831</v>
       </c>
       <c r="L49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2408,31 +2420,31 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>75.96208185780392</v>
+        <v>75.75344870803026</v>
       </c>
       <c r="D50" t="n">
-        <v>8.048957994505374</v>
+        <v>8.148431457500765</v>
       </c>
       <c r="E50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F50" t="n">
-        <v>86.27403893828527</v>
+        <v>87.12027654148683</v>
       </c>
       <c r="G50" t="n">
-        <v>7.241299261066382</v>
+        <v>4.071611671721667</v>
       </c>
       <c r="H50" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I50" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="J50" t="n">
-        <v>1.2424653653803e-05</v>
+        <v>7.013427973251959e-06</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0003727396096140901</v>
+        <v>0.0002104028391975588</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -2448,31 +2460,31 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>66.1991608361643</v>
+        <v>65.90913616323836</v>
       </c>
       <c r="D51" t="n">
-        <v>7.967648414675672</v>
+        <v>8.001606466187519</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F51" t="n">
-        <v>77.08472031880372</v>
+        <v>78.66810974380972</v>
       </c>
       <c r="G51" t="n">
-        <v>6.767298870431322</v>
+        <v>5.35894044590838</v>
       </c>
       <c r="H51" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I51" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="J51" t="n">
-        <v>1.361375319866809e-05</v>
+        <v>2.100162308581315e-06</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0004084125959600426</v>
+        <v>6.300486925743945e-05</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -2488,28 +2500,28 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>75.61883149471079</v>
+        <v>76.4576966687146</v>
       </c>
       <c r="D52" t="n">
-        <v>8.143349939892511</v>
+        <v>7.175295690756179</v>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F52" t="n">
-        <v>76.41176893711649</v>
+        <v>77.44048277908342</v>
       </c>
       <c r="G52" t="n">
-        <v>8.623668813705461</v>
+        <v>8.621388335171266</v>
       </c>
       <c r="H52" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I52" t="n">
-        <v>325</v>
+        <v>266</v>
       </c>
       <c r="J52" t="n">
-        <v>0.6241338988347811</v>
+        <v>0.7587401350491447</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
@@ -2528,31 +2540,31 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>72.81677743722007</v>
+        <v>73.19947871415926</v>
       </c>
       <c r="D53" t="n">
-        <v>9.506636051292972</v>
+        <v>9.51211303389667</v>
       </c>
       <c r="E53" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
-        <v>83.78110920902269</v>
+        <v>84.25342660661664</v>
       </c>
       <c r="G53" t="n">
-        <v>6.465634414626168</v>
+        <v>3.895249301446048</v>
       </c>
       <c r="H53" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I53" t="n">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="J53" t="n">
-        <v>0.000448106693982186</v>
+        <v>0.000370151729784253</v>
       </c>
       <c r="K53" t="n">
-        <v>0.01344320081946558</v>
+        <v>0.01110455189352759</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -2568,31 +2580,31 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>64.75269157239006</v>
+        <v>65.03121437373326</v>
       </c>
       <c r="D54" t="n">
-        <v>7.161289466846886</v>
+        <v>7.175063008371617</v>
       </c>
       <c r="E54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F54" t="n">
-        <v>75.7094137129269</v>
+        <v>75.81937084493296</v>
       </c>
       <c r="G54" t="n">
-        <v>9.215268197530669</v>
+        <v>8.239611638166584</v>
       </c>
       <c r="H54" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I54" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="J54" t="n">
-        <v>7.187263180570752e-05</v>
+        <v>7.186887210782031e-05</v>
       </c>
       <c r="K54" t="n">
-        <v>0.002156178954171225</v>
+        <v>0.002156066163234609</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
@@ -2608,31 +2620,31 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>63.53520463286154</v>
+        <v>62.91517195189908</v>
       </c>
       <c r="D55" t="n">
-        <v>13.98847182866754</v>
+        <v>13.93626756473126</v>
       </c>
       <c r="E55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
-        <v>74.57456970603509</v>
+        <v>75.21344753541487</v>
       </c>
       <c r="G55" t="n">
-        <v>7.279705880275531</v>
+        <v>7.558381118188291</v>
       </c>
       <c r="H55" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I55" t="n">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="J55" t="n">
-        <v>0.01877341106967713</v>
+        <v>0.008038063309718787</v>
       </c>
       <c r="K55" t="n">
-        <v>0.563202332090314</v>
+        <v>0.2411418992915636</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2648,31 +2660,31 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>56.47783028795934</v>
+        <v>55.53343168925968</v>
       </c>
       <c r="D56" t="n">
-        <v>10.65092484278883</v>
+        <v>9.791411568803735</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
-        <v>75.51248694786493</v>
+        <v>74.65472031634951</v>
       </c>
       <c r="G56" t="n">
-        <v>5.119482355879556</v>
+        <v>3.647653560329394</v>
       </c>
       <c r="H56" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I56" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>6.695290165472321e-07</v>
+        <v>4.147716037478125e-07</v>
       </c>
       <c r="K56" t="n">
-        <v>2.008587049641696e-05</v>
+        <v>1.244314811243437e-05</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -2688,34 +2700,34 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>68.97794797617499</v>
+        <v>68.64916249125396</v>
       </c>
       <c r="D57" t="n">
-        <v>10.76709700862475</v>
+        <v>10.86546423454368</v>
       </c>
       <c r="E57" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F57" t="n">
-        <v>79.18412490101944</v>
+        <v>78.98926756622726</v>
       </c>
       <c r="G57" t="n">
-        <v>5.29033988066789</v>
+        <v>5.264295923956753</v>
       </c>
       <c r="H57" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I57" t="n">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="J57" t="n">
-        <v>0.001524389376134469</v>
+        <v>0.002213510676357138</v>
       </c>
       <c r="K57" t="n">
-        <v>0.04573168128403408</v>
+        <v>0.06640532029071412</v>
       </c>
       <c r="L57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2728,31 +2740,31 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>70.02076542986546</v>
+        <v>69.88417580093095</v>
       </c>
       <c r="D58" t="n">
-        <v>8.6017880816008</v>
+        <v>8.752558956717928</v>
       </c>
       <c r="E58" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F58" t="n">
-        <v>78.89769853631564</v>
+        <v>80.6471021681587</v>
       </c>
       <c r="G58" t="n">
-        <v>9.291212311103337</v>
+        <v>6.210455372490167</v>
       </c>
       <c r="H58" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I58" t="n">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0006496287948377549</v>
+        <v>0.0001994170717347799</v>
       </c>
       <c r="K58" t="n">
-        <v>0.01948886384513265</v>
+        <v>0.005982512152043398</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -2768,28 +2780,28 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>77.74270733269628</v>
+        <v>78.12056435966372</v>
       </c>
       <c r="D59" t="n">
-        <v>8.673969127302902</v>
+        <v>8.648887093238008</v>
       </c>
       <c r="E59" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F59" t="n">
-        <v>75.91052439383772</v>
+        <v>75.94394176227529</v>
       </c>
       <c r="G59" t="n">
-        <v>6.019422344326569</v>
+        <v>5.409704511582706</v>
       </c>
       <c r="H59" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I59" t="n">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2340463920462175</v>
+        <v>0.1550482468680151</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -2808,31 +2820,31 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>70.84931376573913</v>
+        <v>71.50909767245402</v>
       </c>
       <c r="D60" t="n">
-        <v>11.09646701375437</v>
+        <v>10.83416783173242</v>
       </c>
       <c r="E60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F60" t="n">
-        <v>77.57146792181305</v>
+        <v>78.75597210321881</v>
       </c>
       <c r="G60" t="n">
-        <v>7.393627097872074</v>
+        <v>7.129418716031313</v>
       </c>
       <c r="H60" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I60" t="n">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="J60" t="n">
-        <v>0.04443118885886295</v>
+        <v>0.03155921403962992</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0.9467764211888976</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2848,31 +2860,31 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>66.97888660731331</v>
+        <v>67.41350139310795</v>
       </c>
       <c r="D61" t="n">
-        <v>9.566589323735046</v>
+        <v>9.51896522520139</v>
       </c>
       <c r="E61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F61" t="n">
-        <v>79.01823755180315</v>
+        <v>80.02133850278031</v>
       </c>
       <c r="G61" t="n">
-        <v>7.214967505298584</v>
+        <v>6.918447036423646</v>
       </c>
       <c r="H61" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I61" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="J61" t="n">
-        <v>5.121763294808298e-05</v>
+        <v>5.931636742376943e-05</v>
       </c>
       <c r="K61" t="n">
-        <v>0.001536528988442489</v>
+        <v>0.001779491022713083</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
@@ -2888,28 +2900,28 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>90.5424495435327</v>
+        <v>90.72699193778958</v>
       </c>
       <c r="D62" t="n">
-        <v>20.11877668221461</v>
+        <v>20.51289822135669</v>
       </c>
       <c r="E62" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F62" t="n">
-        <v>94.06292053438301</v>
+        <v>93.87110266936249</v>
       </c>
       <c r="G62" t="n">
-        <v>11.82956943902812</v>
+        <v>12.41892163108633</v>
       </c>
       <c r="H62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I62" t="n">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="J62" t="n">
-        <v>0.4653901846017948</v>
+        <v>0.5167279184620508</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -2928,31 +2940,31 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>105.8059352980819</v>
+        <v>104.8425568158606</v>
       </c>
       <c r="D63" t="n">
-        <v>13.18550792408894</v>
+        <v>12.56579620172877</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F63" t="n">
-        <v>53.26970582378524</v>
+        <v>48.03870094327783</v>
       </c>
       <c r="G63" t="n">
-        <v>20.14816409675831</v>
+        <v>8.258643710373637</v>
       </c>
       <c r="H63" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I63" t="n">
-        <v>575</v>
+        <v>504</v>
       </c>
       <c r="J63" t="n">
-        <v>4.01933742563528e-08</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K63" t="n">
-        <v>1.205801227690584e-06</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -2968,31 +2980,31 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>109.8079653820227</v>
+        <v>110.2437069189996</v>
       </c>
       <c r="D64" t="n">
-        <v>8.50234422293731</v>
+        <v>8.399712346028831</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
-        <v>111.9232305516407</v>
+        <v>118.9462182085011</v>
       </c>
       <c r="G64" t="n">
-        <v>29.35360334122606</v>
+        <v>22.33258605637223</v>
       </c>
       <c r="H64" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I64" t="n">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="J64" t="n">
-        <v>0.06148381785893191</v>
+        <v>0.006116495991957317</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0.1834948797587195</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -3008,31 +3020,31 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>121.6247312051952</v>
+        <v>122.8203746961986</v>
       </c>
       <c r="D65" t="n">
-        <v>11.08396050122833</v>
+        <v>9.603854467678762</v>
       </c>
       <c r="E65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F65" t="n">
-        <v>41.23116339123414</v>
+        <v>37.12422550847428</v>
       </c>
       <c r="G65" t="n">
-        <v>15.96393712933504</v>
+        <v>8.274213543379691</v>
       </c>
       <c r="H65" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I65" t="n">
-        <v>597</v>
+        <v>504</v>
       </c>
       <c r="J65" t="n">
-        <v>3.029346803845298e-09</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K65" t="n">
-        <v>9.088040411535895e-08</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3048,28 +3060,28 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>105.5669519024566</v>
+        <v>106.3358405837057</v>
       </c>
       <c r="D66" t="n">
-        <v>13.68596281201015</v>
+        <v>13.42870924828801</v>
       </c>
       <c r="E66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F66" t="n">
-        <v>98.6304922849905</v>
+        <v>100.7126981452465</v>
       </c>
       <c r="G66" t="n">
-        <v>16.50533716920259</v>
+        <v>15.96120884873628</v>
       </c>
       <c r="H66" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I66" t="n">
-        <v>385</v>
+        <v>316</v>
       </c>
       <c r="J66" t="n">
-        <v>0.09102795464309961</v>
+        <v>0.1485491888660017</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3088,31 +3100,31 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>125.4484323877209</v>
+        <v>126.310902301227</v>
       </c>
       <c r="D67" t="n">
-        <v>8.385437390803823</v>
+        <v>7.392497308237926</v>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F67" t="n">
-        <v>109.0574522471045</v>
+        <v>112.5755807592317</v>
       </c>
       <c r="G67" t="n">
-        <v>21.83069956966772</v>
+        <v>18.69393590898745</v>
       </c>
       <c r="H67" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I67" t="n">
-        <v>439</v>
+        <v>359</v>
       </c>
       <c r="J67" t="n">
-        <v>0.00560562926553005</v>
+        <v>0.01539466842931958</v>
       </c>
       <c r="K67" t="n">
-        <v>0.1681688779659015</v>
+        <v>0.4618400528795875</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -3128,28 +3140,28 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>94.35066509405038</v>
+        <v>93.66516476727303</v>
       </c>
       <c r="D68" t="n">
-        <v>20.52920610403748</v>
+        <v>20.67028983301892</v>
       </c>
       <c r="E68" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F68" t="n">
-        <v>91.93166830055331</v>
+        <v>91.00899316101648</v>
       </c>
       <c r="G68" t="n">
-        <v>13.72205478186316</v>
+        <v>12.65999885971932</v>
       </c>
       <c r="H68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I68" t="n">
-        <v>314</v>
+        <v>264</v>
       </c>
       <c r="J68" t="n">
-        <v>0.7871602536039209</v>
+        <v>0.7936035829324073</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -3168,31 +3180,31 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>74.23807928435754</v>
+        <v>74.50603772236174</v>
       </c>
       <c r="D69" t="n">
-        <v>14.6940319321268</v>
+        <v>14.93706704513481</v>
       </c>
       <c r="E69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F69" t="n">
-        <v>52.43973580816122</v>
+        <v>52.58042917246547</v>
       </c>
       <c r="G69" t="n">
-        <v>19.16628016317719</v>
+        <v>20.3297632186797</v>
       </c>
       <c r="H69" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I69" t="n">
-        <v>498</v>
+        <v>408</v>
       </c>
       <c r="J69" t="n">
-        <v>7.815119319557491e-05</v>
+        <v>0.0004035557789410014</v>
       </c>
       <c r="K69" t="n">
-        <v>0.002344535795867248</v>
+        <v>0.01210667336823004</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
@@ -3208,31 +3220,31 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>103.45590999326</v>
+        <v>104.8883300272652</v>
       </c>
       <c r="D70" t="n">
-        <v>17.49460753180448</v>
+        <v>16.35598262742231</v>
       </c>
       <c r="E70" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
-        <v>53.89103500347196</v>
+        <v>48.9019718242054</v>
       </c>
       <c r="G70" t="n">
-        <v>18.72171280955433</v>
+        <v>12.66602135471397</v>
       </c>
       <c r="H70" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I70" t="n">
-        <v>578</v>
+        <v>504</v>
       </c>
       <c r="J70" t="n">
-        <v>2.856695978784544e-08</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K70" t="n">
-        <v>8.570087936353631e-07</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
@@ -3248,31 +3260,31 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>116.3567142944668</v>
+        <v>116.5476443947467</v>
       </c>
       <c r="D71" t="n">
-        <v>15.11678511453133</v>
+        <v>15.3989410120972</v>
       </c>
       <c r="E71" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F71" t="n">
-        <v>79.70419851469462</v>
+        <v>80.38746444107927</v>
       </c>
       <c r="G71" t="n">
-        <v>24.43764117097955</v>
+        <v>25.12833992982081</v>
       </c>
       <c r="H71" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I71" t="n">
-        <v>535</v>
+        <v>445</v>
       </c>
       <c r="J71" t="n">
-        <v>2.73205048921227e-06</v>
+        <v>1.189373797518411e-05</v>
       </c>
       <c r="K71" t="n">
-        <v>8.19615146763681e-05</v>
+        <v>0.0003568121392555233</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
@@ -3288,31 +3300,31 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>120.7623791434344</v>
+        <v>120.6681837561011</v>
       </c>
       <c r="D72" t="n">
-        <v>11.85681652320079</v>
+        <v>12.09214412512015</v>
       </c>
       <c r="E72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F72" t="n">
-        <v>71.03628690286536</v>
+        <v>67.71767318470795</v>
       </c>
       <c r="G72" t="n">
-        <v>19.33068915597385</v>
+        <v>15.26953663540908</v>
       </c>
       <c r="H72" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I72" t="n">
-        <v>583</v>
+        <v>502</v>
       </c>
       <c r="J72" t="n">
-        <v>1.604478370132695e-08</v>
+        <v>1.37621980788932e-08</v>
       </c>
       <c r="K72" t="n">
-        <v>4.813435110398085e-07</v>
+        <v>4.12865942366796e-07</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
@@ -3328,31 +3340,31 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>51.52634746645423</v>
+        <v>52.81738174744191</v>
       </c>
       <c r="D73" t="n">
-        <v>21.47391157598876</v>
+        <v>20.94453016354884</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
-        <v>103.2848995670197</v>
+        <v>106.3133781047493</v>
       </c>
       <c r="G73" t="n">
-        <v>13.50226098010623</v>
+        <v>11.27071698045282</v>
       </c>
       <c r="H73" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J73" t="n">
-        <v>1.427975195843672e-08</v>
+        <v>2.332724399288526e-08</v>
       </c>
       <c r="K73" t="n">
-        <v>4.283925587531017e-07</v>
+        <v>6.998173197865578e-07</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
@@ -3368,31 +3380,31 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>125.4109577844489</v>
+        <v>125.2163860338413</v>
       </c>
       <c r="D74" t="n">
-        <v>5.610274492893797</v>
+        <v>5.642711366073894</v>
       </c>
       <c r="E74" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F74" t="n">
-        <v>87.54264342462659</v>
+        <v>90.97339280973078</v>
       </c>
       <c r="G74" t="n">
-        <v>17.25292930289677</v>
+        <v>13.36885441177339</v>
       </c>
       <c r="H74" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I74" t="n">
-        <v>599</v>
+        <v>503</v>
       </c>
       <c r="J74" t="n">
-        <v>2.372535872451451e-09</v>
+        <v>1.204611101179206e-08</v>
       </c>
       <c r="K74" t="n">
-        <v>7.117607617354352e-08</v>
+        <v>3.613833303537619e-07</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
@@ -3408,31 +3420,31 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>85.39872801911635</v>
+        <v>84.23059708351195</v>
       </c>
       <c r="D75" t="n">
-        <v>18.10478677415369</v>
+        <v>17.53076423725072</v>
       </c>
       <c r="E75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F75" t="n">
-        <v>64.71181325694904</v>
+        <v>64.39377066064459</v>
       </c>
       <c r="G75" t="n">
-        <v>20.30169088174146</v>
+        <v>13.42482187451711</v>
       </c>
       <c r="H75" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I75" t="n">
-        <v>476</v>
+        <v>405</v>
       </c>
       <c r="J75" t="n">
-        <v>0.000448106693982186</v>
+        <v>0.0005214375143108174</v>
       </c>
       <c r="K75" t="n">
-        <v>0.01344320081946558</v>
+        <v>0.01564312542932452</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
@@ -3448,31 +3460,31 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>85.24832191654909</v>
+        <v>86.10968256642757</v>
       </c>
       <c r="D76" t="n">
-        <v>17.77151465052761</v>
+        <v>17.61924022062777</v>
       </c>
       <c r="E76" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F76" t="n">
-        <v>103.0136128939196</v>
+        <v>101.5475891416548</v>
       </c>
       <c r="G76" t="n">
-        <v>10.89454359860357</v>
+        <v>8.275708620588194</v>
       </c>
       <c r="H76" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I76" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0003061970051475102</v>
+        <v>0.001010851986690264</v>
       </c>
       <c r="K76" t="n">
-        <v>0.009185910154425304</v>
+        <v>0.03032555960070792</v>
       </c>
       <c r="L76" t="b">
         <v>1</v>
@@ -3488,31 +3500,31 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>68.98134624103911</v>
+        <v>69.03262763464245</v>
       </c>
       <c r="D77" t="n">
-        <v>15.84846507319481</v>
+        <v>16.17323954949573</v>
       </c>
       <c r="E77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F77" t="n">
-        <v>93.47468496619872</v>
+        <v>95.72680493433795</v>
       </c>
       <c r="G77" t="n">
-        <v>19.83547127881477</v>
+        <v>16.83555142791842</v>
       </c>
       <c r="H77" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I77" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="J77" t="n">
-        <v>4.313731889636114e-05</v>
+        <v>8.676272436234233e-06</v>
       </c>
       <c r="K77" t="n">
-        <v>0.001294119566890834</v>
+        <v>0.000260288173087027</v>
       </c>
       <c r="L77" t="b">
         <v>1</v>
@@ -3528,31 +3540,31 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>101.3093953801847</v>
+        <v>102.7702280931516</v>
       </c>
       <c r="D78" t="n">
-        <v>13.48176987603107</v>
+        <v>11.66107064408448</v>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F78" t="n">
-        <v>76.7957754452341</v>
+        <v>74.77582737402291</v>
       </c>
       <c r="G78" t="n">
-        <v>14.65819638092756</v>
+        <v>14.44920782732668</v>
       </c>
       <c r="H78" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I78" t="n">
-        <v>532</v>
+        <v>467</v>
       </c>
       <c r="J78" t="n">
-        <v>3.65665732704832e-06</v>
+        <v>1.06062188881748e-06</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0001096997198114496</v>
+        <v>3.181865666452441e-05</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
@@ -3568,28 +3580,28 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>107.8712759022114</v>
+        <v>108.1211234758895</v>
       </c>
       <c r="D79" t="n">
-        <v>11.96600742698297</v>
+        <v>12.14869515888021</v>
       </c>
       <c r="E79" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F79" t="n">
-        <v>89.2478211864058</v>
+        <v>94.57026501060537</v>
       </c>
       <c r="G79" t="n">
-        <v>40.68586619503494</v>
+        <v>40.6110587381235</v>
       </c>
       <c r="H79" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I79" t="n">
-        <v>323</v>
+        <v>240</v>
       </c>
       <c r="J79" t="n">
-        <v>0.6527104405758399</v>
+        <v>0.7936035829324073</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
@@ -3608,31 +3620,31 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>84.51061871208856</v>
+        <v>83.53436868145322</v>
       </c>
       <c r="D80" t="n">
-        <v>14.08943842094212</v>
+        <v>13.52616045860866</v>
       </c>
       <c r="E80" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F80" t="n">
-        <v>113.5328331469677</v>
+        <v>113.2591374390571</v>
       </c>
       <c r="G80" t="n">
-        <v>16.09906654427477</v>
+        <v>14.09233777170844</v>
       </c>
       <c r="H80" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I80" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="J80" t="n">
-        <v>2.245198370872341e-06</v>
+        <v>1.495832779679567e-06</v>
       </c>
       <c r="K80" t="n">
-        <v>6.735595112617022e-05</v>
+        <v>4.4874983390387e-05</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
@@ -3648,31 +3660,31 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>87.76191857116584</v>
+        <v>86.94614230388238</v>
       </c>
       <c r="D81" t="n">
-        <v>15.88159335379718</v>
+        <v>15.68748258355819</v>
       </c>
       <c r="E81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F81" t="n">
-        <v>49.7505380976451</v>
+        <v>51.65433527065623</v>
       </c>
       <c r="G81" t="n">
-        <v>9.141109966773733</v>
+        <v>7.097140951517649</v>
       </c>
       <c r="H81" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I81" t="n">
-        <v>600</v>
+        <v>504</v>
       </c>
       <c r="J81" t="n">
-        <v>2.098410375666297e-09</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K81" t="n">
-        <v>6.295231126998892e-08</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -3688,31 +3700,31 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>114.0179156301693</v>
+        <v>114.4145097446026</v>
       </c>
       <c r="D82" t="n">
-        <v>11.63842937420091</v>
+        <v>11.71173525161598</v>
       </c>
       <c r="E82" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F82" t="n">
-        <v>55.97228851377552</v>
+        <v>56.60142607683332</v>
       </c>
       <c r="G82" t="n">
-        <v>37.76213673318546</v>
+        <v>39.62350908132237</v>
       </c>
       <c r="H82" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I82" t="n">
-        <v>512</v>
+        <v>421</v>
       </c>
       <c r="J82" t="n">
-        <v>2.336913118941477e-05</v>
+        <v>0.0001263288254205339</v>
       </c>
       <c r="K82" t="n">
-        <v>0.000701073935682443</v>
+        <v>0.003789864762616017</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
@@ -3728,28 +3740,28 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>99.14855848293578</v>
+        <v>98.79464742509619</v>
       </c>
       <c r="D83" t="n">
-        <v>21.94741423648829</v>
+        <v>22.32998075232744</v>
       </c>
       <c r="E83" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F83" t="n">
-        <v>103.9874134550576</v>
+        <v>105.3788602764183</v>
       </c>
       <c r="G83" t="n">
-        <v>13.72023097586884</v>
+        <v>12.35295648546219</v>
       </c>
       <c r="H83" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I83" t="n">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="J83" t="n">
-        <v>0.5028577901906203</v>
+        <v>0.406310544288517</v>
       </c>
       <c r="K83" t="n">
         <v>1</v>
@@ -3768,31 +3780,31 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>76.82147331658595</v>
+        <v>77.84209473224676</v>
       </c>
       <c r="D84" t="n">
-        <v>16.5599597049362</v>
+        <v>16.11263193799677</v>
       </c>
       <c r="E84" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F84" t="n">
-        <v>63.0158976548618</v>
+        <v>64.51060093481662</v>
       </c>
       <c r="G84" t="n">
-        <v>13.50222524041443</v>
+        <v>12.95014507676114</v>
       </c>
       <c r="H84" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I84" t="n">
-        <v>441</v>
+        <v>375</v>
       </c>
       <c r="J84" t="n">
-        <v>0.004954149997571722</v>
+        <v>0.005320315775777456</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1486244999271517</v>
+        <v>0.1596094732733237</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3808,31 +3820,31 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>66.27798168004405</v>
+        <v>64.70237258235805</v>
       </c>
       <c r="D85" t="n">
-        <v>19.79647921948554</v>
+        <v>18.6055416475414</v>
       </c>
       <c r="E85" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
-        <v>49.83473413598019</v>
+        <v>50.79738483286209</v>
       </c>
       <c r="G85" t="n">
-        <v>15.44796555292745</v>
+        <v>16.08861774192414</v>
       </c>
       <c r="H85" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I85" t="n">
-        <v>442</v>
+        <v>359</v>
       </c>
       <c r="J85" t="n">
-        <v>0.004654800413463103</v>
+        <v>0.01539466842931958</v>
       </c>
       <c r="K85" t="n">
-        <v>0.1396440124038931</v>
+        <v>0.4618400528795875</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3848,28 +3860,28 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>47.32334856932781</v>
+        <v>45.58618638053219</v>
       </c>
       <c r="D86" t="n">
-        <v>14.08619653512222</v>
+        <v>11.4562279978758</v>
       </c>
       <c r="E86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F86" t="n">
-        <v>65.20643228049741</v>
+        <v>59.29214793386252</v>
       </c>
       <c r="G86" t="n">
-        <v>27.9613580182327</v>
+        <v>23.42056618264784</v>
       </c>
       <c r="H86" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I86" t="n">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="J86" t="n">
-        <v>0.04443118885886295</v>
+        <v>0.094488261319036</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -3888,34 +3900,34 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>87.69711690460136</v>
+        <v>87.99817770561435</v>
       </c>
       <c r="D87" t="n">
-        <v>11.93550991649</v>
+        <v>12.08826455807075</v>
       </c>
       <c r="E87" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F87" t="n">
-        <v>74.02672177205231</v>
+        <v>68.03548867803963</v>
       </c>
       <c r="G87" t="n">
-        <v>20.64153647564953</v>
+        <v>13.96877654743909</v>
       </c>
       <c r="H87" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I87" t="n">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="J87" t="n">
-        <v>0.005270804155809905</v>
+        <v>0.0001048827399110266</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1581241246742972</v>
+        <v>0.003146482197330799</v>
       </c>
       <c r="L87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -3928,28 +3940,28 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>102.900092151216</v>
+        <v>102.7049840568386</v>
       </c>
       <c r="D88" t="n">
-        <v>20.31030399798244</v>
+        <v>20.70614935951656</v>
       </c>
       <c r="E88" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F88" t="n">
-        <v>92.59155286900283</v>
+        <v>98.06585001502559</v>
       </c>
       <c r="G88" t="n">
-        <v>35.38159078309732</v>
+        <v>33.59180531740975</v>
       </c>
       <c r="H88" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I88" t="n">
-        <v>343</v>
+        <v>259</v>
       </c>
       <c r="J88" t="n">
-        <v>0.3953250862453848</v>
+        <v>0.8824373772892935</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -3968,31 +3980,31 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>121.4248435757608</v>
+        <v>121.7245271301795</v>
       </c>
       <c r="D89" t="n">
-        <v>9.769111308941291</v>
+        <v>9.857320153251411</v>
       </c>
       <c r="E89" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
-        <v>71.71845826185067</v>
+        <v>68.11969548434521</v>
       </c>
       <c r="G89" t="n">
-        <v>21.60898185579853</v>
+        <v>17.41337524267335</v>
       </c>
       <c r="H89" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I89" t="n">
-        <v>576</v>
+        <v>497</v>
       </c>
       <c r="J89" t="n">
-        <v>3.588336987169417e-08</v>
+        <v>2.658339904849052e-08</v>
       </c>
       <c r="K89" t="n">
-        <v>1.076501096150825e-06</v>
+        <v>7.975019714547155e-07</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -4008,31 +4020,31 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>107.3019613381531</v>
+        <v>108.4404429109733</v>
       </c>
       <c r="D90" t="n">
-        <v>19.84015610101395</v>
+        <v>19.43269439825597</v>
       </c>
       <c r="E90" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F90" t="n">
-        <v>81.72260571758241</v>
+        <v>86.00855631511813</v>
       </c>
       <c r="G90" t="n">
-        <v>32.91444443296334</v>
+        <v>31.6935128658989</v>
       </c>
       <c r="H90" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I90" t="n">
-        <v>423</v>
+        <v>345</v>
       </c>
       <c r="J90" t="n">
-        <v>0.01428562147054283</v>
+        <v>0.03533939760922535</v>
       </c>
       <c r="K90" t="n">
-        <v>0.4285686441162849</v>
+        <v>1</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -4048,31 +4060,31 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>71.97597665584208</v>
+        <v>72.19797800124574</v>
       </c>
       <c r="D91" t="n">
-        <v>15.18330706251713</v>
+        <v>15.45659187241596</v>
       </c>
       <c r="E91" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F91" t="n">
-        <v>88.11642592365648</v>
+        <v>91.21518573791853</v>
       </c>
       <c r="G91" t="n">
-        <v>14.32134619439219</v>
+        <v>12.54589710452404</v>
       </c>
       <c r="H91" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I91" t="n">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0006035812492172734</v>
+        <v>0.0001385419277881577</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0181074374765182</v>
+        <v>0.004156257833644732</v>
       </c>
       <c r="L91" t="b">
         <v>1</v>
@@ -4088,28 +4100,28 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>11.08004182509503</v>
+        <v>10.99890471596388</v>
       </c>
       <c r="D92" t="n">
-        <v>3.869185448973475</v>
+        <v>3.928077151932428</v>
       </c>
       <c r="E92" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F92" t="n">
-        <v>12.70178817178362</v>
+        <v>12.12463591872247</v>
       </c>
       <c r="G92" t="n">
-        <v>2.533847107465117</v>
+        <v>1.996039429702046</v>
       </c>
       <c r="H92" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I92" t="n">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="J92" t="n">
-        <v>0.2262788928879548</v>
+        <v>0.4192903869887252</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4128,31 +4140,31 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>8.032284887350302</v>
+        <v>7.966935285549421</v>
       </c>
       <c r="D93" t="n">
-        <v>2.135817772086552</v>
+        <v>2.155231973358657</v>
       </c>
       <c r="E93" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F93" t="n">
-        <v>17.61262284111756</v>
+        <v>17.38250930302313</v>
       </c>
       <c r="G93" t="n">
-        <v>2.630313570300171</v>
+        <v>2.608023171201833</v>
       </c>
       <c r="H93" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>2.098410375666297e-09</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K93" t="n">
-        <v>6.295231126998892e-08</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
@@ -4168,31 +4180,31 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>10.21972992452186</v>
+        <v>10.01249030512833</v>
       </c>
       <c r="D94" t="n">
-        <v>3.172352030819819</v>
+        <v>3.067480503050926</v>
       </c>
       <c r="E94" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F94" t="n">
-        <v>14.92807634829649</v>
+        <v>14.44225754713662</v>
       </c>
       <c r="G94" t="n">
-        <v>3.353348899489797</v>
+        <v>3.076440867455898</v>
       </c>
       <c r="H94" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I94" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J94" t="n">
-        <v>3.956591173644805e-05</v>
+        <v>0.0001048827399110266</v>
       </c>
       <c r="K94" t="n">
-        <v>0.001186977352093442</v>
+        <v>0.003146482197330799</v>
       </c>
       <c r="L94" t="b">
         <v>1</v>
@@ -4208,31 +4220,31 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>10.03859883094033</v>
+        <v>9.820186910031564</v>
       </c>
       <c r="D95" t="n">
-        <v>3.183915831630431</v>
+        <v>3.060574158114505</v>
       </c>
       <c r="E95" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F95" t="n">
-        <v>19.07661727011326</v>
+        <v>18.9882358981842</v>
       </c>
       <c r="G95" t="n">
-        <v>1.547325981558704</v>
+        <v>1.209743085294944</v>
       </c>
       <c r="H95" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>2.098410375666297e-09</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K95" t="n">
-        <v>6.295231126998892e-08</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -4248,34 +4260,34 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>12.27683235911693</v>
+        <v>12.05733062349844</v>
       </c>
       <c r="D96" t="n">
-        <v>3.855686802803567</v>
+        <v>3.779050866670112</v>
       </c>
       <c r="E96" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F96" t="n">
-        <v>15.97254435994926</v>
+        <v>15.66124517283216</v>
       </c>
       <c r="G96" t="n">
-        <v>2.335497893504857</v>
+        <v>2.301139223617022</v>
       </c>
       <c r="H96" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I96" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="J96" t="n">
-        <v>0.001001873827571444</v>
+        <v>0.001899688427521008</v>
       </c>
       <c r="K96" t="n">
-        <v>0.03005621482714333</v>
+        <v>0.05699065282563025</v>
       </c>
       <c r="L96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4288,31 +4300,31 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>7.902998013733599</v>
+        <v>7.539671355674087</v>
       </c>
       <c r="D97" t="n">
-        <v>3.356700746889762</v>
+        <v>2.904610138284775</v>
       </c>
       <c r="E97" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F97" t="n">
-        <v>12.86077076594211</v>
+        <v>12.27235407698062</v>
       </c>
       <c r="G97" t="n">
-        <v>2.427972560542321</v>
+        <v>1.962274913281921</v>
       </c>
       <c r="H97" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I97" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="J97" t="n">
-        <v>4.026689709618671e-06</v>
+        <v>3.660450528326813e-06</v>
       </c>
       <c r="K97" t="n">
-        <v>0.0001208006912885601</v>
+        <v>0.0001098135158498044</v>
       </c>
       <c r="L97" t="b">
         <v>1</v>
@@ -4328,31 +4340,31 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>9.773800295102406</v>
+        <v>9.639283974613598</v>
       </c>
       <c r="D98" t="n">
-        <v>2.064353028027798</v>
+        <v>1.996685287769455</v>
       </c>
       <c r="E98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F98" t="n">
-        <v>16.84938390272964</v>
+        <v>16.44954180752938</v>
       </c>
       <c r="G98" t="n">
-        <v>2.249794444849841</v>
+        <v>2.023704532391554</v>
       </c>
       <c r="H98" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>2.372535872451451e-09</v>
+        <v>1.204611101179206e-08</v>
       </c>
       <c r="K98" t="n">
-        <v>7.117607617354352e-08</v>
+        <v>3.613833303537619e-07</v>
       </c>
       <c r="L98" t="b">
         <v>1</v>
@@ -4368,31 +4380,31 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>10.79743754610972</v>
+        <v>10.60302172597087</v>
       </c>
       <c r="D99" t="n">
-        <v>4.304708654070116</v>
+        <v>4.284586756806779</v>
       </c>
       <c r="E99" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F99" t="n">
-        <v>16.38934722773958</v>
+        <v>16.21799206033921</v>
       </c>
       <c r="G99" t="n">
-        <v>2.420501679009287</v>
+        <v>1.975244724999235</v>
       </c>
       <c r="H99" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I99" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="J99" t="n">
-        <v>3.319350288742911e-06</v>
+        <v>4.555453055095883e-06</v>
       </c>
       <c r="K99" t="n">
-        <v>9.958050866228733e-05</v>
+        <v>0.0001366635916528765</v>
       </c>
       <c r="L99" t="b">
         <v>1</v>
@@ -4408,31 +4420,31 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29061892060607</v>
+        <v>11.03262342044528</v>
       </c>
       <c r="D100" t="n">
-        <v>3.797740007668085</v>
+        <v>3.655097594935844</v>
       </c>
       <c r="E100" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F100" t="n">
-        <v>17.44655276374775</v>
+        <v>17.27295806410635</v>
       </c>
       <c r="G100" t="n">
-        <v>2.592112815055781</v>
+        <v>2.434215054177197</v>
       </c>
       <c r="H100" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I100" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="J100" t="n">
-        <v>1.667813131845819e-06</v>
+        <v>2.100162308581315e-06</v>
       </c>
       <c r="K100" t="n">
-        <v>5.003439395537458e-05</v>
+        <v>6.300486925743945e-05</v>
       </c>
       <c r="L100" t="b">
         <v>1</v>
@@ -4448,31 +4460,31 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>11.13476108052887</v>
+        <v>10.86179517100804</v>
       </c>
       <c r="D101" t="n">
-        <v>2.629393247935978</v>
+        <v>2.310632026190378</v>
       </c>
       <c r="E101" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F101" t="n">
-        <v>18.03749905415883</v>
+        <v>17.55073822900702</v>
       </c>
       <c r="G101" t="n">
-        <v>3.607857314440913</v>
+        <v>3.574040504260066</v>
       </c>
       <c r="H101" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I101" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J101" t="n">
-        <v>4.904798361307395e-07</v>
+        <v>1.190013259012667e-06</v>
       </c>
       <c r="K101" t="n">
-        <v>1.471439508392218e-05</v>
+        <v>3.570039777038002e-05</v>
       </c>
       <c r="L101" t="b">
         <v>1</v>
@@ -4488,31 +4500,31 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>10.04199489245784</v>
+        <v>10.06303528696817</v>
       </c>
       <c r="D102" t="n">
-        <v>3.782980917462367</v>
+        <v>3.859555223869822</v>
       </c>
       <c r="E102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F102" t="n">
-        <v>18.97139037464763</v>
+        <v>18.98576319921301</v>
       </c>
       <c r="G102" t="n">
-        <v>2.139552276338365</v>
+        <v>1.291355394008513</v>
       </c>
       <c r="H102" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>3.861956188370621e-09</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K102" t="n">
-        <v>1.158586856511186e-07</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -4528,28 +4540,28 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>15.02293785823729</v>
+        <v>14.95796404148455</v>
       </c>
       <c r="D103" t="n">
-        <v>2.348773420962029</v>
+        <v>2.375091721539321</v>
       </c>
       <c r="E103" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F103" t="n">
-        <v>14.39660762253366</v>
+        <v>13.73041135982223</v>
       </c>
       <c r="G103" t="n">
-        <v>2.965216925145453</v>
+        <v>1.902883884393437</v>
       </c>
       <c r="H103" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I103" t="n">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="J103" t="n">
-        <v>0.170686901643934</v>
+        <v>0.0900880009523822</v>
       </c>
       <c r="K103" t="n">
         <v>1</v>
@@ -4568,31 +4580,31 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>9.715406106350349</v>
+        <v>9.580238777594888</v>
       </c>
       <c r="D104" t="n">
-        <v>2.800265068637799</v>
+        <v>2.776951170709332</v>
       </c>
       <c r="E104" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F104" t="n">
-        <v>15.66363471378843</v>
+        <v>15.05044555873534</v>
       </c>
       <c r="G104" t="n">
-        <v>4.504717299742444</v>
+        <v>4.486830052455108</v>
       </c>
       <c r="H104" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I104" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="J104" t="n">
-        <v>6.607329525880471e-05</v>
+        <v>0.0002607116415805983</v>
       </c>
       <c r="K104" t="n">
-        <v>0.001982198857764142</v>
+        <v>0.007821349247417949</v>
       </c>
       <c r="L104" t="b">
         <v>1</v>
@@ -4608,31 +4620,31 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>13.83678400771802</v>
+        <v>13.95971290174597</v>
       </c>
       <c r="D105" t="n">
-        <v>1.778126452375894</v>
+        <v>1.707537630427338</v>
       </c>
       <c r="E105" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F105" t="n">
-        <v>17.28188495497791</v>
+        <v>17.00797560270343</v>
       </c>
       <c r="G105" t="n">
-        <v>1.962515379237519</v>
+        <v>1.787092402322926</v>
       </c>
       <c r="H105" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I105" t="n">
         <v>47</v>
       </c>
       <c r="J105" t="n">
-        <v>4.418100645390863e-07</v>
+        <v>3.278773194246992e-06</v>
       </c>
       <c r="K105" t="n">
-        <v>1.325430193617259e-05</v>
+        <v>9.836319582740976e-05</v>
       </c>
       <c r="L105" t="b">
         <v>1</v>
@@ -4648,31 +4660,31 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>11.58658101129331</v>
+        <v>11.32951042080469</v>
       </c>
       <c r="D106" t="n">
-        <v>3.133142286365553</v>
+        <v>2.928049276458065</v>
       </c>
       <c r="E106" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F106" t="n">
-        <v>14.86045402739151</v>
+        <v>14.70976182368975</v>
       </c>
       <c r="G106" t="n">
-        <v>2.006278119409455</v>
+        <v>1.196612003468851</v>
       </c>
       <c r="H106" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I106" t="n">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="J106" t="n">
-        <v>0.0002834212197516381</v>
+        <v>0.0001048827399110266</v>
       </c>
       <c r="K106" t="n">
-        <v>0.008502636592549144</v>
+        <v>0.003146482197330799</v>
       </c>
       <c r="L106" t="b">
         <v>1</v>
@@ -4688,31 +4700,31 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>13.50454786901987</v>
+        <v>13.43930998524483</v>
       </c>
       <c r="D107" t="n">
-        <v>2.8419233277164</v>
+        <v>2.882126068025411</v>
       </c>
       <c r="E107" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F107" t="n">
-        <v>17.6437419603503</v>
+        <v>17.49834970989697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.712930988168271</v>
+        <v>2.86527277132491</v>
       </c>
       <c r="H107" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I107" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J107" t="n">
-        <v>2.336913118941477e-05</v>
+        <v>0.0001151357224721427</v>
       </c>
       <c r="K107" t="n">
-        <v>0.000701073935682443</v>
+        <v>0.003454071674164281</v>
       </c>
       <c r="L107" t="b">
         <v>1</v>
@@ -4728,31 +4740,31 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>9.98837619885362</v>
+        <v>9.622214379622781</v>
       </c>
       <c r="D108" t="n">
-        <v>4.116841429979022</v>
+        <v>3.781891597205522</v>
       </c>
       <c r="E108" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F108" t="n">
-        <v>16.56565639010267</v>
+        <v>16.53008876043461</v>
       </c>
       <c r="G108" t="n">
-        <v>2.60605219530258</v>
+        <v>2.64685694797781</v>
       </c>
       <c r="H108" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I108" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J108" t="n">
-        <v>4.43246009623508e-06</v>
+        <v>3.278773194246992e-06</v>
       </c>
       <c r="K108" t="n">
-        <v>0.0001329738028870524</v>
+        <v>9.836319582740976e-05</v>
       </c>
       <c r="L108" t="b">
         <v>1</v>
@@ -4768,34 +4780,34 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>11.01355598433683</v>
+        <v>10.9928401599417</v>
       </c>
       <c r="D109" t="n">
-        <v>4.219981788245948</v>
+        <v>4.305755209116266</v>
       </c>
       <c r="E109" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F109" t="n">
-        <v>16.08020147598504</v>
+        <v>15.43293148597041</v>
       </c>
       <c r="G109" t="n">
-        <v>3.899986314065011</v>
+        <v>3.562943286353621</v>
       </c>
       <c r="H109" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I109" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J109" t="n">
-        <v>0.000448106693982186</v>
+        <v>0.003461466561763674</v>
       </c>
       <c r="K109" t="n">
-        <v>0.01344320081946558</v>
+        <v>0.1038439968529102</v>
       </c>
       <c r="L109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -4808,31 +4820,31 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>12.26363866976899</v>
+        <v>12.15445254715015</v>
       </c>
       <c r="D110" t="n">
-        <v>2.82139389153911</v>
+        <v>2.827348740846806</v>
       </c>
       <c r="E110" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F110" t="n">
-        <v>17.53984651362952</v>
+        <v>17.33801950324419</v>
       </c>
       <c r="G110" t="n">
-        <v>2.894241447681984</v>
+        <v>2.261119713697261</v>
       </c>
       <c r="H110" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I110" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J110" t="n">
-        <v>8.22296167687859e-07</v>
+        <v>1.876490836430798e-06</v>
       </c>
       <c r="K110" t="n">
-        <v>2.466888503063577e-05</v>
+        <v>5.629472509292394e-05</v>
       </c>
       <c r="L110" t="b">
         <v>1</v>
@@ -4848,31 +4860,31 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>12.06555082004422</v>
+        <v>12.05072008068021</v>
       </c>
       <c r="D111" t="n">
-        <v>2.810474345983773</v>
+        <v>2.867469708774713</v>
       </c>
       <c r="E111" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F111" t="n">
-        <v>16.67415128492513</v>
+        <v>15.57056332946885</v>
       </c>
       <c r="G111" t="n">
-        <v>3.311167264007976</v>
+        <v>1.62861159502279</v>
       </c>
       <c r="H111" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I111" t="n">
         <v>62</v>
       </c>
       <c r="J111" t="n">
-        <v>2.034166485137406e-06</v>
+        <v>1.623164138508973e-05</v>
       </c>
       <c r="K111" t="n">
-        <v>6.102499455412219e-05</v>
+        <v>0.0004869492415526919</v>
       </c>
       <c r="L111" t="b">
         <v>1</v>
@@ -4888,31 +4900,31 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>9.961309233301151</v>
+        <v>9.84875438633825</v>
       </c>
       <c r="D112" t="n">
-        <v>2.43123763161539</v>
+        <v>2.416710525949692</v>
       </c>
       <c r="E112" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F112" t="n">
-        <v>19.69380757807914</v>
+        <v>19.30522084039332</v>
       </c>
       <c r="G112" t="n">
-        <v>3.208279917749289</v>
+        <v>3.204858772793592</v>
       </c>
       <c r="H112" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I112" t="n">
         <v>2</v>
       </c>
       <c r="J112" t="n">
-        <v>2.681424888183732e-09</v>
+        <v>1.37621980788932e-08</v>
       </c>
       <c r="K112" t="n">
-        <v>8.044274664551197e-08</v>
+        <v>4.12865942366796e-07</v>
       </c>
       <c r="L112" t="b">
         <v>1</v>
@@ -4928,31 +4940,31 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>8.983467623857882</v>
+        <v>8.916468867638976</v>
       </c>
       <c r="D113" t="n">
-        <v>2.837766365005669</v>
+        <v>2.876844687601976</v>
       </c>
       <c r="E113" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F113" t="n">
-        <v>14.94680719501347</v>
+        <v>14.04867501168783</v>
       </c>
       <c r="G113" t="n">
-        <v>3.276501704819343</v>
+        <v>1.891333570477154</v>
       </c>
       <c r="H113" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I113" t="n">
         <v>32</v>
       </c>
       <c r="J113" t="n">
-        <v>8.795423188011772e-08</v>
+        <v>5.920334682008857e-07</v>
       </c>
       <c r="K113" t="n">
-        <v>2.638626956403532e-06</v>
+        <v>1.776100404602657e-05</v>
       </c>
       <c r="L113" t="b">
         <v>1</v>
@@ -4968,31 +4980,31 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>15.88642216673282</v>
+        <v>15.81028005173746</v>
       </c>
       <c r="D114" t="n">
-        <v>2.655037881325344</v>
+        <v>2.682909496363306</v>
       </c>
       <c r="E114" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F114" t="n">
-        <v>19.42262741662407</v>
+        <v>19.48303721749749</v>
       </c>
       <c r="G114" t="n">
-        <v>1.94050163641145</v>
+        <v>1.455852401502417</v>
       </c>
       <c r="H114" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I114" t="n">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="J114" t="n">
-        <v>1.491093418271024e-05</v>
+        <v>1.071204570040937e-05</v>
       </c>
       <c r="K114" t="n">
-        <v>0.0004473280254813072</v>
+        <v>0.0003213613710122809</v>
       </c>
       <c r="L114" t="b">
         <v>1</v>
@@ -5008,31 +5020,31 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>12.08331087906472</v>
+        <v>12.14686051680757</v>
       </c>
       <c r="D115" t="n">
-        <v>2.915357496004216</v>
+        <v>2.958459617234329</v>
       </c>
       <c r="E115" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F115" t="n">
-        <v>17.84800273821004</v>
+        <v>17.0103877002818</v>
       </c>
       <c r="G115" t="n">
-        <v>2.949129179821588</v>
+        <v>2.070663997276958</v>
       </c>
       <c r="H115" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I115" t="n">
         <v>51</v>
       </c>
       <c r="J115" t="n">
-        <v>6.695290165472321e-07</v>
+        <v>5.078150611178878e-06</v>
       </c>
       <c r="K115" t="n">
-        <v>2.008587049641696e-05</v>
+        <v>0.0001523445183353663</v>
       </c>
       <c r="L115" t="b">
         <v>1</v>
@@ -5048,31 +5060,31 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>14.26415776630152</v>
+        <v>14.31993389752752</v>
       </c>
       <c r="D116" t="n">
-        <v>1.657329907678127</v>
+        <v>1.668357157048335</v>
       </c>
       <c r="E116" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F116" t="n">
-        <v>19.36524447628772</v>
+        <v>19.52571444785844</v>
       </c>
       <c r="G116" t="n">
-        <v>2.022153590322239</v>
+        <v>1.720282388470395</v>
       </c>
       <c r="H116" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>3.861956188370621e-09</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K116" t="n">
-        <v>1.158586856511186e-07</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L116" t="b">
         <v>1</v>
@@ -5088,31 +5100,31 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>8.844224902105424</v>
+        <v>8.672017881126671</v>
       </c>
       <c r="D117" t="n">
-        <v>3.632835575717914</v>
+        <v>3.606384403390377</v>
       </c>
       <c r="E117" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F117" t="n">
-        <v>18.64712091869544</v>
+        <v>18.66880845636019</v>
       </c>
       <c r="G117" t="n">
-        <v>2.605191600893052</v>
+        <v>2.517951559207566</v>
       </c>
       <c r="H117" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I117" t="n">
         <v>3</v>
       </c>
       <c r="J117" t="n">
-        <v>3.029346803845298e-09</v>
+        <v>1.571483740174675e-08</v>
       </c>
       <c r="K117" t="n">
-        <v>9.088040411535895e-08</v>
+        <v>4.714451220524026e-07</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -5128,31 +5140,31 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>11.20847247128143</v>
+        <v>11.10540865781854</v>
       </c>
       <c r="D118" t="n">
-        <v>2.552506789942876</v>
+        <v>2.553665527484496</v>
       </c>
       <c r="E118" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F118" t="n">
-        <v>17.1550674702663</v>
+        <v>16.54785121062685</v>
       </c>
       <c r="G118" t="n">
-        <v>4.160688812638453</v>
+        <v>3.93673670783148</v>
       </c>
       <c r="H118" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I118" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J118" t="n">
-        <v>2.336913118941477e-05</v>
+        <v>0.0001151357224721427</v>
       </c>
       <c r="K118" t="n">
-        <v>0.000701073935682443</v>
+        <v>0.003454071674164281</v>
       </c>
       <c r="L118" t="b">
         <v>1</v>
@@ -5168,31 +5180,31 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>9.923644300910754</v>
+        <v>9.752104963715231</v>
       </c>
       <c r="D119" t="n">
-        <v>2.555382269219711</v>
+        <v>2.463009820514107</v>
       </c>
       <c r="E119" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F119" t="n">
-        <v>20.93123244191366</v>
+        <v>21.13085360038144</v>
       </c>
       <c r="G119" t="n">
-        <v>2.11263013443959</v>
+        <v>1.758939455139288</v>
       </c>
       <c r="H119" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>2.098410375666297e-09</v>
+        <v>1.053869950790467e-08</v>
       </c>
       <c r="K119" t="n">
-        <v>6.295231126998892e-08</v>
+        <v>3.1616098523714e-07</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
@@ -5208,34 +5220,34 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>12.23494525418204</v>
+        <v>11.94994776838196</v>
       </c>
       <c r="D120" t="n">
-        <v>4.935990302353761</v>
+        <v>4.832036606838426</v>
       </c>
       <c r="E120" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F120" t="n">
-        <v>18.57276324735473</v>
+        <v>17.52952766766554</v>
       </c>
       <c r="G120" t="n">
-        <v>5.618156580269714</v>
+        <v>5.228341013578226</v>
       </c>
       <c r="H120" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I120" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="J120" t="n">
-        <v>0.001327349722879934</v>
+        <v>0.004002372980595459</v>
       </c>
       <c r="K120" t="n">
-        <v>0.03982049168639803</v>
+        <v>0.1200711894178638</v>
       </c>
       <c r="L120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5248,31 +5260,31 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>13.93599813028509</v>
+        <v>13.71420145233403</v>
       </c>
       <c r="D121" t="n">
-        <v>2.809203077869384</v>
+        <v>2.643973402757164</v>
       </c>
       <c r="E121" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F121" t="n">
-        <v>18.1013976236679</v>
+        <v>17.68401758017612</v>
       </c>
       <c r="G121" t="n">
-        <v>2.11361995656384</v>
+        <v>1.777589867381981</v>
       </c>
       <c r="H121" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I121" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="J121" t="n">
-        <v>3.65665732704832e-06</v>
+        <v>5.658004990938262e-06</v>
       </c>
       <c r="K121" t="n">
-        <v>0.0001096997198114496</v>
+        <v>0.0001697401497281479</v>
       </c>
       <c r="L121" t="b">
         <v>1</v>
